--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5907625B-B0F5-412B-9FB2-727255F89F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD50B1C3-540C-4672-AA35-42613FD40168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="156">
   <si>
     <t>IMP*Z</t>
   </si>
@@ -605,7 +605,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -673,6 +673,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -813,7 +819,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -848,7 +854,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3699,95 +3706,95 @@
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="27"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D6" t="s">
+      <c r="C5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" t="s">
         <v>147</v>
       </c>
-      <c r="E6">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="28">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28">
+        <v>15</v>
+      </c>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C8" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="29">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C9" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
         <v>1</v>
       </c>
-      <c r="F6">
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C10" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="29">
+        <v>0</v>
+      </c>
+      <c r="F10" s="29">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:8" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="26">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C11" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="29">
         <v>0</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F11" s="29">
         <v>15</v>
       </c>
-      <c r="G7" s="26"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="16">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" s="16">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" s="16">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="16">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
     </row>
     <row r="21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD50B1C3-540C-4672-AA35-42613FD40168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8577689-7C8C-49F4-A06B-BC4F23422592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="149">
   <si>
     <t>IMP*Z</t>
   </si>
@@ -325,9 +325,6 @@
     <t>W</t>
   </si>
   <si>
-    <t>TH$2022</t>
-  </si>
-  <si>
     <t>* Wet Season (W(June 08 to September 05</t>
   </si>
   <si>
@@ -403,12 +400,6 @@
     <t>_24</t>
   </si>
   <si>
-    <t>_25</t>
-  </si>
-  <si>
-    <t>_26</t>
-  </si>
-  <si>
     <t>~Milestoneyears</t>
   </si>
   <si>
@@ -577,12 +568,6 @@
     <t>ACT_BND</t>
   </si>
   <si>
-    <t>Share-O</t>
-  </si>
-  <si>
-    <t>Share-I</t>
-  </si>
-  <si>
     <t>msy09/2050</t>
   </si>
   <si>
@@ -592,13 +577,7 @@
     <t>~TFM_UPD</t>
   </si>
   <si>
-    <t>NCAP_BND</t>
-  </si>
-  <si>
-    <t>UP,LO</t>
-  </si>
-  <si>
-    <t>FX</t>
+    <t>TH$2024</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1353,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>the start year of the model (2005);</a:t>
+            <a:t>the start year of the model (2022);</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3286,16 +3265,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:J30"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:J28"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3305,7 +3284,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
@@ -3322,7 +3301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="16" t="s">
         <v>58</v>
       </c>
@@ -3333,135 +3312,125 @@
         <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H6" t="s">
         <v>62</v>
       </c>
       <c r="J6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J7" t="s">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J8" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J9" t="s">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J10" t="s">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J11" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J12" t="s">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J13" t="s">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J14" t="s">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J15" t="s">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="J16" t="s">
+    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J17" t="s">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J18" t="s">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J19" t="s">
+    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J20" t="s">
+    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J21" t="s">
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J22" t="s">
+    <row r="23" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J23" t="s">
+    <row r="24" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J24" t="s">
+    <row r="25" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J25" t="s">
+    <row r="26" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J26" t="s">
+    <row r="27" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J27" t="s">
+    <row r="28" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J30" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3477,109 +3446,109 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:D22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="13"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2022</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="13"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="24"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="23" t="s">
         <v>92</v>
-      </c>
-      <c r="C13" s="13"/>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="24"/>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="C15" s="23"/>
       <c r="D15" s="24"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="15">
         <v>2022</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C17">
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C18">
         <v>2030</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C19">
         <v>2035</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C20">
         <v>2040</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C21">
         <v>2045</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C22">
         <v>2050</v>
@@ -3597,18 +3566,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:C9"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.44140625" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>30</v>
       </c>
@@ -3616,7 +3585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>32</v>
       </c>
@@ -3624,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
         <v>33</v>
       </c>
@@ -3632,7 +3601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>34</v>
       </c>
@@ -3640,7 +3609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>35</v>
       </c>
@@ -3648,7 +3617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
         <v>57</v>
       </c>
@@ -3668,23 +3637,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AA11A5-2377-4878-AD2C-E80254AFF82E}">
   <dimension ref="B3:Q39"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
@@ -3705,12 +3674,12 @@
       </c>
       <c r="H4" s="27"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3719,103 +3688,63 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:8" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="28">
-        <v>0</v>
-      </c>
-      <c r="F7" s="28">
-        <v>15</v>
-      </c>
+    <row r="7" spans="2:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C8" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="29">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C9" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C10" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" s="29">
-        <v>0</v>
-      </c>
-      <c r="F10" s="29">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C11" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="29">
-        <v>0</v>
-      </c>
-      <c r="F11" s="29">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
       <c r="E12" s="29"/>
       <c r="F12" s="29"/>
     </row>
-    <row r="21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="2:17" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="2:17" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="5" t="s">
         <v>18</v>
       </c>
@@ -3826,7 +3755,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>2</v>
@@ -3865,12 +3794,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>3</v>
       </c>
       <c r="G38">
-        <v>2222</v>
+        <v>9999999</v>
       </c>
       <c r="J38" t="s">
         <v>16</v>
@@ -3879,12 +3808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
         <v>3</v>
       </c>
       <c r="G39">
-        <v>8888</v>
+        <v>9999999</v>
       </c>
       <c r="J39" t="s">
         <v>16</v>
@@ -3904,29 +3833,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:G59"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="11"/>
-    <col min="2" max="2" width="12.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="11"/>
+    <col min="2" max="2" width="12.109375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="11" customWidth="1"/>
     <col min="4" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="36.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="11"/>
+    <col min="5" max="5" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="36.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
@@ -3946,7 +3875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
         <v>54</v>
       </c>
@@ -3954,7 +3883,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
         <v>44</v>
       </c>
@@ -3962,7 +3891,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>62</v>
       </c>
@@ -3973,7 +3902,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>63</v>
       </c>
@@ -3985,9 +3914,9 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>53</v>
@@ -3997,12 +3926,12 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>53</v>
@@ -4013,9 +3942,9 @@
       </c>
       <c r="F12" s="17"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>53</v>
@@ -4025,9 +3954,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>53</v>
@@ -4037,9 +3966,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15"/>
       <c r="D15" s="11" t="s">
@@ -4051,9 +3980,9 @@
       </c>
       <c r="F15" s="17"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C16"/>
       <c r="D16" s="11" t="s">
@@ -4065,9 +3994,9 @@
       </c>
       <c r="F16" s="17"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17"/>
       <c r="D17" s="11" t="s">
@@ -4079,9 +4008,9 @@
       </c>
       <c r="F17" s="17"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C18"/>
       <c r="D18" s="11" t="s">
@@ -4092,9 +4021,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C19"/>
       <c r="D19" s="11" t="s">
@@ -4105,9 +4034,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C20"/>
       <c r="D20" s="11" t="s">
@@ -4118,9 +4047,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C21"/>
       <c r="D21" s="11" t="s">
@@ -4131,9 +4060,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C22"/>
       <c r="D22" s="11" t="s">
@@ -4144,9 +4073,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C23"/>
       <c r="D23" s="11" t="s">
@@ -4157,9 +4086,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C24"/>
       <c r="D24" s="11" t="s">
@@ -4170,9 +4099,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="11" t="s">
@@ -4183,9 +4112,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C26"/>
       <c r="D26" s="11" t="s">
@@ -4196,9 +4125,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="11" t="s">
@@ -4209,9 +4138,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C28"/>
       <c r="D28" s="11" t="s">
@@ -4222,9 +4151,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="11" t="s">
@@ -4235,9 +4164,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C30"/>
       <c r="D30" s="11" t="s">
@@ -4248,9 +4177,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="11" t="s">
@@ -4261,9 +4190,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C32"/>
       <c r="D32" s="11" t="s">
@@ -4274,9 +4203,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C33"/>
       <c r="D33" s="11" t="s">
@@ -4287,9 +4216,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="11" t="s">
@@ -4300,9 +4229,9 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="11" t="s">
@@ -4313,9 +4242,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="11" t="s">
@@ -4326,9 +4255,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>53</v>
@@ -4338,9 +4267,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>53</v>
@@ -4350,9 +4279,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>53</v>
@@ -4362,9 +4291,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>53</v>
@@ -4374,9 +4303,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>53</v>
@@ -4386,9 +4315,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>53</v>
@@ -4398,9 +4327,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>53</v>
@@ -4410,9 +4339,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>53</v>
@@ -4422,9 +4351,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>53</v>
@@ -4434,9 +4363,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>53</v>
@@ -4446,9 +4375,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>53</v>
@@ -4458,9 +4387,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>53</v>
@@ -4470,9 +4399,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>53</v>
@@ -4482,9 +4411,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>53</v>
@@ -4494,9 +4423,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>53</v>
@@ -4506,9 +4435,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>53</v>
@@ -4518,9 +4447,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>53</v>
@@ -4530,9 +4459,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>53</v>
@@ -4542,9 +4471,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>53</v>
@@ -4554,9 +4483,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>53</v>
@@ -4566,9 +4495,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>53</v>
@@ -4578,9 +4507,9 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>53</v>
@@ -4590,7 +4519,7 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E59" s="17"/>
     </row>
   </sheetData>
@@ -4605,13 +4534,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:E6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
@@ -4619,7 +4548,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
         <v>47</v>
       </c>
@@ -4630,31 +4559,31 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4667,18 +4596,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:H7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="10" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:8" ht="15" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>39</v>
       </c>
@@ -4689,7 +4618,7 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="4" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
@@ -4698,12 +4627,12 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
@@ -4726,7 +4655,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>40</v>
       </c>
